--- a/Data/IPJudicialSystem.xlsx
+++ b/Data/IPJudicialSystem.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,146 +472,146 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>Which article states the conditions for removal of High Court judges?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 227</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The President appoints CJI after consultation with senior judges.</t>
+          <t>It provides the removal process for High Court judges.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
+          <t>What role does the PM play in judicial accountability?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>Can remove judges</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>Direct supervision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PM influences appointments by advising the President.</t>
+          <t>PM can initiate impeachment recommendation to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
+          <t>Which constitutional article provides immunity to judges from executive interference?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parliamentary Committee</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Article 211</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Union Cabinet</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The Collegium system recommends judges’ appointments.</t>
+          <t>It mandates separation of judiciary from executive.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The appointment of High Court judges involves consultation with</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chief Justice of India only</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>State Governor only</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -621,102 +621,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Both are consulted for High Court appointments.</t>
+          <t>On the advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The PM’s role in judicial appointments is</t>
+          <t>Which article protects judges from arbitrary removal by the executive?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Decisive</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Constitutionally mandated</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Non-existent</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PM advises President but actual appointment is collegium-based.</t>
+          <t>Separation of judiciary from executive ensures protection.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which landmark case established the Collegium system?</t>
+          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Always approved</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Never questioned</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Controlled by legislature</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>It reinforced judiciary’s primacy in appointments.</t>
+          <t>Judiciary can invalidate unconstitutional executive actions.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The President appoints Supreme Court judges after consultation with</t>
+          <t>Who has the final say in appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Consultation is constitutionally mandated.</t>
+          <t>President appoints judges but follows collegium recommendations.</t>
         </is>
       </c>
     </row>
@@ -792,11 +792,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
+          <t>The President appoints Supreme Court judges after consultation with</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -806,597 +806,597 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
+          <t>Consultation is constitutionally mandated.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Supreme Court’s power of judicial review limits the</t>
+          <t>Which landmark case established the Collegium system?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>President’s powers</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Parliament’s legislative powers</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Judicial review can check executive actions including PM’s decisions.</t>
+          <t>It reinforced judiciary’s primacy in appointments.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which article provides for the removal of Supreme Court judges?</t>
+          <t>Which of the following is NOT a feature of the collegium system?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Confidential recommendations</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Collegium consists of CJI and senior judges</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>No formal legal backing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>It describes the impeachment process.</t>
+          <t>The executive has no formal role in selection.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
+          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Consultation</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Only in consultation with Cabinet</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No involvement</t>
+          <t>Only with President’s approval</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cabinet advises President on appointments.</t>
+          <t>The PM cannot veto; President follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
+          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Only for Chief Justice</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Only with Parliament approval</t>
+          <t>No involvement</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Appointments require consultation and collegium recommendations.</t>
+          <t>Cabinet advises President on appointments.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The role of the PM in judiciary is</t>
+          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PM’s role is advisory via President.</t>
+          <t>It provides for President’s appointment after consultation.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
+          <t>Who appoints the Registrar General of the Supreme Court?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Parliamentary approval</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Public opinion</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Supreme Court can review executive actions.</t>
+          <t>CJI appoints administrative officers.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Appointment of Attorney General is done by</t>
+          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial appointments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>President appoints AG on PM’s advice.</t>
+          <t>It upheld the collegium system against NJAC.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The collegium system was challenged in which case?</t>
+          <t>What is the role of the Prime Minister in judicial impeachments?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Can impeach judges</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Decides final removal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>The NJAC case questioned collegium’s legitimacy.</t>
+          <t>PM can recommend initiating impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The PM’s influence on judiciary appointments has</t>
+          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Increased over time</t>
+          <t>Parliamentary approval</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Remained constant</t>
+          <t>Public opinion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Never existed</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Collegium system reduces direct PM influence.</t>
+          <t>Supreme Court can review executive actions.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who acts as the constitutional head of the judiciary?</t>
+          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CJI is head of judiciary as per convention.</t>
+          <t>Added anti-defection law which can involve judicial scrutiny.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which body was proposed to replace the collegium system?</t>
+          <t>The Supreme Court’s power of judicial review limits the</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>President’s powers</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Supreme Judicial Council</t>
+          <t>Parliament’s legislative powers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Parliamentary Judicial Panel</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NJAC was proposed but struck down by SC.</t>
+          <t>Judicial review can check executive actions including PM’s decisions.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The PM can influence judiciary appointments through</t>
+          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Control over Collegium</t>
+          <t>Basic Structure Doctrine</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Control over Parliament</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Control over Election Commission</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>President acts on PM’s advice.</t>
+          <t>These principles collectively limit executive control.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Prime Minister is accountable to the judiciary in matters of</t>
+          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Budgetary sanctions</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Foreign policy</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Election conduct</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Judiciary can review legality of executive acts.</t>
+          <t>The collegium consists of the CJI and four senior-most judges.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The principle of separation of powers implies the PM should</t>
+          <t>Which case emphasized the independence of the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Directly control judiciary</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Influence judiciary indirectly</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Appoint judges directly</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Separation mandates judicial independence.</t>
+          <t>Known as the Judges’ Transfer case affirming independence.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who has the final say in appointment of Supreme Court judges?</t>
+          <t>Who is the custodian of judicial independence in India?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1411,837 +1411,837 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>President appoints judges but follows collegium recommendations.</t>
+          <t>CJI safeguards judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of the following is true regarding the PM and judiciary?</t>
+          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PM can remove judges directly</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PM heads judiciary</t>
+          <t>Article 247</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PM appoints judges by executive order</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
+          <t>Parliament can legislate on judiciary subject under this article.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
+          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Cabinet’s consensus</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Parliament’s decision</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 130</t>
+          <t>Supreme Court order</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
+          <t>Executive follows collegium’s advice.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
+          <t>Which article provides for the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PM advises the President via Cabinet for appointments.</t>
+          <t>It describes the impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about the collegium system?</t>
+          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>It consists of the CJI and four senior judges</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>It was created by a Supreme Court judgment</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>It recommends appointments of judges</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The PM is not part of the collegium.</t>
+          <t>PM influences appointments by advising the President.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
+          <t>The Prime Minister’s influence on judicial appointments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Has increased over years</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Remains constant</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yes, thrice</t>
+          <t>Is absolute</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The President can send back recommendations once for reconsideration.</t>
+          <t>Collegium limits executive role.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who is the final authority in the appointment of High Court judges?</t>
+          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Appointment is made by the President after consultation.</t>
+          <t>It was added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
+          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Judicial appointments</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>60 days</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>It upheld the collegium system against NJAC.</t>
+          <t>The Constitution does not specify a time limit.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
+          <t>The Prime Minister’s office can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Direct orders</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Article 311(2)</t>
+          <t>Parliamentary resolution</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Impeachment procedure is mentioned in Article 124(4).</t>
+          <t>PM influences President through Cabinet advice.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
+          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Initiate impeachment</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Judicial Selection Committee</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Preside over proceedings</t>
+          <t>Judicial Review Board</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The PM may advise the President to initiate proceedings.</t>
+          <t>NJAC was declared unconstitutional.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
+          <t>The Supreme Court can review actions of the Prime Minister under</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 131</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Judicial Selection Committee</t>
+          <t>Article 142</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Judicial Review Board</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>NJAC was declared unconstitutional.</t>
+          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who is the appointing authority for the Attorney General of India?</t>
+          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Executive privilege</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Parliamentary oversight</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Appointed by the President on PM’s advice.</t>
+          <t>Courts check constitutionality of executive actions.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Multiple principles safeguard judicial independence.</t>
+          <t>The President appoints CJI after consultation with senior judges.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which article states the conditions for removal of High Court judges?</t>
+          <t>Who is responsible for the administration of the Supreme Court?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Article 227</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>It provides the removal process for High Court judges.</t>
+          <t>CJI oversees the administration of the Supreme Court.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
+          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>If unpopular</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Only in consultation with Cabinet</t>
+          <t>If advised by Parliament</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Only with President’s approval</t>
+          <t>If voted by Lok Sabha</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The PM cannot veto; President follows collegium recommendations.</t>
+          <t>Judiciary ensures constitutional compliance.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
+          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seniority</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Political affiliation</t>
+          <t>Basic structure of the Constitution</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Executive preference</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Judges are appointed based on merit and integrity.</t>
+          <t>It was struck down as it compromised judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What role does the PM play in judicial accountability?</t>
+          <t>The Prime Minister is accountable to the judiciary in matters of</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Can remove judges</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>Budgetary sanctions</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Direct supervision</t>
+          <t>Foreign policy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Election conduct</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>PM can initiate impeachment recommendation to Parliament.</t>
+          <t>Judiciary can review legality of executive acts.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who is responsible for the administration of the Supreme Court?</t>
+          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CJI oversees the administration of the Supreme Court.</t>
+          <t>Collegium protects judicial independence under basic structure.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
+          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Constitutional provisions</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>It tried to curtail judiciary’s power but was struck down.</t>
+          <t>These collectively protect judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
+          <t>The collegium system was challenged in which case?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Only for High Court appointments</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The collegium is independent of the executive.</t>
+          <t>The NJAC case questioned collegium’s legitimacy.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The removal of a Supreme Court judge requires a</t>
+          <t>The role of the PM in judiciary is</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Simple majority in Parliament</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Majority in Supreme Court</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Impeachment requires two-thirds majority in both Houses.</t>
+          <t>PM’s role is advisory via President.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who appoints the Lokpal and Lokayuktas?</t>
+          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2256,67 +2256,67 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Central Government</t>
+          <t>No formal body</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Appointments are made by the President based on recommendations.</t>
+          <t>Judicial appointments can be challenged in SC.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
+          <t>The removal of a Supreme Court judge requires a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Controlling court procedures</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Appointing judges</t>
+          <t>Simple majority in Parliament</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Impeachment of judges</t>
+          <t>Majority in Supreme Court</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Judicial independence limits executive interference.</t>
+          <t>Impeachment requires two-thirds majority in both Houses.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
+          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2346,447 +2346,447 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI before appointment.</t>
+          <t>It requires consultation with CJI and Governor.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Supreme Court can review actions of the Prime Minister under</t>
+          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 131</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 142</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
+          <t>After the S.P. Gupta case, judicial independence increased.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
+          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Controlling court procedures</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Appointing judges</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Impeachment of judges</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Parliament does not participate in appointments.</t>
+          <t>Judicial independence limits executive interference.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
+          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Always approved</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Never questioned</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Controlled by legislature</t>
+          <t>S. R. Bommai</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Judiciary can invalidate unconstitutional executive actions.</t>
+          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
+          <t>Who appoints the Lokpal and Lokayuktas?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S. P. Gupta Case</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Central Government</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
+          <t>Appointments are made by the President based on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
+          <t>Who is the appointing authority for the Attorney General of India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>The collegium consists of the CJI and four senior-most judges.</t>
+          <t>Appointed by the President on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
+          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The Constitution does not specify a time limit.</t>
+          <t>It requires consultation with CJI before appointment.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
+          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It mandates consultation with CJI, Governor, and others.</t>
+          <t>The senior-most puisne judge acts as CJI.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
+          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Direct appointment authority</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Basic Structure Doctrine</t>
+          <t>Consults the Collegium</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>These principles collectively limit executive control.</t>
+          <t>PM recommends to President but must follow Collegium advice.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
+          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Initiate impeachment</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Basic structure of the Constitution</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Preside over proceedings</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>It was struck down as it compromised judiciary’s independence.</t>
+          <t>The PM may advise the President to initiate proceedings.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
+          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PM can remove judges by ordinance</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>Inefficiency</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>President can remove judges on PM advice</t>
+          <t>Unpopularity</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PM can suspend judges</t>
+          <t>Opposition protests</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Removal requires a two-thirds majority in Parliament.</t>
+          <t>Judicial review protects Constitution.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
+          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>After the S.P. Gupta case, judicial independence increased.</t>
+          <t>Multiple principles safeguard judicial independence.</t>
         </is>
       </c>
     </row>
@@ -2796,357 +2796,357 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
+          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Can override judicial orders</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Approves court judgments</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Executive actions including PM’s are subject to judicial review.</t>
+          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>PM can remove judges by ordinance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prime Minister directly</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>President can remove judges on PM advice</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>PM can suspend judges</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The President appoints AG following PM’s advice.</t>
+          <t>Removal requires a two-thirds majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
+          <t>The PM can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Control over Collegium</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Control over Parliament</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Control over Election Commission</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>It provides for President’s appointment after consultation.</t>
+          <t>President acts on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>In the impeachment process of a judge, who investigates the charges?</t>
+          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, thrice</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>A committee constituted by Parliament investigates.</t>
+          <t>The President can send back recommendations once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
+          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Seniority</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>Political affiliation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>S. R. Bommai</t>
+          <t>Executive preference</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
+          <t>Judges are appointed based on merit and integrity.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
+          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Only for Chief Justice</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No formal body</t>
+          <t>Only with Parliament approval</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Judicial appointments can be challenged in SC.</t>
+          <t>Appointments require consultation and collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
+          <t>The appointment of High Court judges involves consultation with</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct appointment authority</t>
+          <t>Chief Justice of India only</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Consults the Collegium</t>
+          <t>State Governor only</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>PM recommends to President but must follow Collegium advice.</t>
+          <t>Both are consulted for High Court appointments.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Who acts as the guardian of the independence of the judiciary?</t>
+          <t>In the impeachment process of a judge, who investigates the charges?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Parliamentary committee</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Attorney General</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CJI protects judiciary’s independence.</t>
+          <t>A committee constituted by Parliament investigates.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
+          <t>Which of the following is true about the NJAC?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>It was accepted</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>It replaced the collegium system</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>It empowered PM</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Added anti-defection law which can involve judicial scrutiny.</t>
+          <t>It was struck down for undermining judicial independence.</t>
         </is>
       </c>
     </row>
@@ -3156,37 +3156,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
+          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cabinet’s consensus</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Parliament’s decision</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Supreme Court order</t>
+          <t>Only for High Court appointments</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Executive follows collegium’s advice.</t>
+          <t>The collegium is independent of the executive.</t>
         </is>
       </c>
     </row>
@@ -3196,1277 +3196,1277 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a feature of the collegium system?</t>
+          <t>Who acts as the constitutional head of the judiciary?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Confidential recommendations</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Collegium consists of CJI and senior judges</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>No formal legal backing</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>The executive has no formal role in selection.</t>
+          <t>CJI is head of judiciary as per convention.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
+          <t>Under which Article can a Supreme Court judge be removed?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Article 247</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Parliament can legislate on judiciary subject under this article.</t>
+          <t>It outlines the impeachment procedure.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Who appoints the Registrar General of the Supreme Court?</t>
+          <t>Which of the following is true regarding the PM and judiciary?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>PM can remove judges directly</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>PM heads judiciary</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>PM appoints judges by executive order</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CJI appoints administrative officers.</t>
+          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which case emphasized the independence of the judiciary from the executive?</t>
+          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>No, never</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Known as the Judges’ Transfer case affirming independence.</t>
+          <t>The President can send recommendations back once on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
+          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>If unpopular</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>If advised by Parliament</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>If voted by Lok Sabha</t>
+          <t>Article 130</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Judiciary ensures constitutional compliance.</t>
+          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which body consults the Prime Minister on judicial appointments?</t>
+          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Article 148</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>There is no formal role for PM in collegium consultations.</t>
+          <t>It mandates consultation before appointment.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which constitutional article provides immunity to judges from executive interference?</t>
+          <t>Who is the final authority in the appointment of High Court judges?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 211</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>It mandates separation of judiciary from executive.</t>
+          <t>Appointment is made by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
+          <t>The PM’s influence on judiciary appointments has</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Increased over time</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Remained constant</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Never existed</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
+          <t>Collegium system reduces direct PM influence.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
+          <t>The collegium system is criticized for</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Excessive executive control</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 148</t>
+          <t>Political interference</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Parliamentary involvement</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>It mandates consultation before appointment.</t>
+          <t>Its opaque functioning is often criticized.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
+          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Collegium protects judicial independence under basic structure.</t>
+          <t>It mandates consultation with CJI, Governor, and others.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
+          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Appointing judges directly</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>No, never</t>
+          <t>Forming judiciary</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Removing judges directly</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>The President can send recommendations back once on PM’s advice.</t>
+          <t>Judiciary is independent from executive.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
+          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>S. P. Gupta Case</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>The NJAC was struck down for violating judicial independence.</t>
+          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in judicial impeachments?</t>
+          <t>The President can reject collegium recommendations for judicial appointments</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Can impeach judges</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>Multiple times</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Decides final removal</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>PM can recommend initiating impeachment proceedings.</t>
+          <t>Rejection can be sent back once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Under which Article can a Supreme Court judge be removed?</t>
+          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Parliamentary Committee</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Union Cabinet</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>It outlines the impeachment procedure.</t>
+          <t>The Collegium system recommends judges’ appointments.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which body nominates the members of the collegium?</t>
+          <t>Which of the following is NOT true about the collegium system?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It consists of the CJI and four senior judges</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>It was created by a Supreme Court judgment</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>It recommends appointments of judges</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Collegium is composed of judges only.</t>
+          <t>The PM is not part of the collegium.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
+          <t>Which body consults the Prime Minister on judicial appointments?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Appointing judges directly</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Forming judiciary</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Removing judges directly</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Judiciary is independent from executive.</t>
+          <t>There is no formal role for PM in collegium consultations.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Three-fourths majority</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Unanimous approval</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>On the advice of the PM.</t>
+          <t>It requires a special majority.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
+          <t>Who acts as the guardian of the independence of the judiciary?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI and Governor.</t>
+          <t>CJI protects judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Executive privilege</t>
+          <t>Prime Minister directly</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Parliamentary oversight</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Courts check constitutionality of executive actions.</t>
+          <t>The President appoints AG following PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The President can reject collegium recommendations for judicial appointments</t>
+          <t>The principle of separation of powers implies the PM should</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Directly control judiciary</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Multiple times</t>
+          <t>Influence judiciary indirectly</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Appoint judges directly</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Rejection can be sent back once for reconsideration.</t>
+          <t>Separation mandates judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
+          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>It was added by the 52nd Amendment.</t>
+          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
+          <t>Appointment of Attorney General is done by</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Constitutional provisions</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>These collectively protect judicial independence.</t>
+          <t>President appoints AG on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
+          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>The senior-most puisne judge acts as CJI.</t>
+          <t>It tried to curtail judiciary’s power but was struck down.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judicial appointments</t>
+          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Has increased over years</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Remains constant</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Is absolute</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Collegium limits executive role.</t>
+          <t>Parliament does not participate in appointments.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which of the following is true about the NJAC?</t>
+          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>It was accepted</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>It replaced the collegium system</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>It empowered PM</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>It was struck down for undermining judicial independence.</t>
+          <t>The NJAC was struck down for violating judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
+          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Inefficiency</t>
+          <t>Can override judicial orders</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Unpopularity</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Opposition protests</t>
+          <t>Approves court judgments</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Judicial review protects Constitution.</t>
+          <t>Executive actions including PM’s are subject to judicial review.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
+          <t>The PM’s role in judicial appointments is</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Decisive</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Constitutionally mandated</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Non-existent</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>But President acts on collegium recommendations.</t>
+          <t>PM advises President but actual appointment is collegium-based.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which article protects judges from arbitrary removal by the executive?</t>
+          <t>Which body was proposed to replace the collegium system?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Supreme Judicial Council</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Parliamentary Judicial Panel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive ensures protection.</t>
+          <t>NJAC was proposed but struck down by SC.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Who is the custodian of judicial independence in India?</t>
+          <t>Which body nominates the members of the collegium?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>CJI safeguards judicial independence.</t>
+          <t>Collegium is composed of judges only.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
+          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Three-fourths majority</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unanimous approval</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>It requires a special majority.</t>
+          <t>But President acts on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The collegium system is criticized for</t>
+          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Excessive executive control</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Political interference</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Parliamentary involvement</t>
+          <t>Article 311(2)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Its opaque functioning is often criticized.</t>
+          <t>Impeachment procedure is mentioned in Article 124(4).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Prime Minister’s office can influence judiciary appointments through</t>
+          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct orders</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Parliamentary resolution</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PM influences President through Cabinet advice.</t>
+          <t>PM advises the President via Cabinet for appointments.</t>
         </is>
       </c>
     </row>

--- a/Data/IPJudicialSystem.xlsx
+++ b/Data/IPJudicialSystem.xlsx
@@ -472,251 +472,251 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which article states the conditions for removal of High Court judges?</t>
+          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Article 227</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It provides the removal process for High Court judges.</t>
+          <t>The NJAC was struck down for violating judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What role does the PM play in judicial accountability?</t>
+          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Can remove judges</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Direct supervision</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PM can initiate impeachment recommendation to Parliament.</t>
+          <t>It requires consultation with CJI and Governor.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which constitutional article provides immunity to judges from executive interference?</t>
+          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Article 211</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>No formal body</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>It mandates separation of judiciary from executive.</t>
+          <t>Judicial appointments can be challenged in SC.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Basic structure of the Constitution</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>On the advice of the PM.</t>
+          <t>It was struck down as it compromised judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which article protects judges from arbitrary removal by the executive?</t>
+          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Executive privilege</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Parliamentary oversight</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive ensures protection.</t>
+          <t>Courts check constitutionality of executive actions.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
+          <t>The PM’s influence on judiciary appointments has</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Always approved</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>Increased over time</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Never questioned</t>
+          <t>Remained constant</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Controlled by legislature</t>
+          <t>Never existed</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Judiciary can invalidate unconstitutional executive actions.</t>
+          <t>Collegium system reduces direct PM influence.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who has the final say in appointment of Supreme Court judges?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -746,1527 +746,1527 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>President appoints judges but follows collegium recommendations.</t>
+          <t>On the advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The PM can recommend removal of a Supreme Court judge under</t>
+          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Only for High Court appointments</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
+          <t>The collegium is independent of the executive.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The President appoints Supreme Court judges after consultation with</t>
+          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Controlling court procedures</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Appointing judges</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>Impeachment of judges</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Consultation is constitutionally mandated.</t>
+          <t>Judicial independence limits executive interference.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which landmark case established the Collegium system?</t>
+          <t>The PM’s role in judicial appointments is</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Decisive</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Constitutionally mandated</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Non-existent</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It reinforced judiciary’s primacy in appointments.</t>
+          <t>PM advises President but actual appointment is collegium-based.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a feature of the collegium system?</t>
+          <t>The collegium system is criticized for</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Confidential recommendations</t>
+          <t>Excessive executive control</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Collegium consists of CJI and senior judges</t>
+          <t>Political interference</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>No formal legal backing</t>
+          <t>Parliamentary involvement</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The executive has no formal role in selection.</t>
+          <t>Its opaque functioning is often criticized.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
+          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always approved</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Only in consultation with Cabinet</t>
+          <t>Never questioned</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Only with President’s approval</t>
+          <t>Controlled by legislature</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The PM cannot veto; President follows collegium recommendations.</t>
+          <t>Judiciary can invalidate unconstitutional executive actions.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
+          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consultation</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>No involvement</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cabinet advises President on appointments.</t>
+          <t>The collegium consists of the CJI and four senior-most judges.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
+          <t>Who is the final authority in the appointment of High Court judges?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>It provides for President’s appointment after consultation.</t>
+          <t>Appointment is made by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who appoints the Registrar General of the Supreme Court?</t>
+          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial appointments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CJI appoints administrative officers.</t>
+          <t>It upheld the collegium system against NJAC.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
+          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Judicial appointments</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>It upheld the collegium system against NJAC.</t>
+          <t>Added anti-defection law which can involve judicial scrutiny.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in judicial impeachments?</t>
+          <t>Who has the final say in appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Can impeach judges</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Decides final removal</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>PM can recommend initiating impeachment proceedings.</t>
+          <t>President appoints judges but follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
+          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>Judicial review</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Parliamentary approval</t>
-        </is>
-      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Public opinion</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Supreme Court can review executive actions.</t>
+          <t>Multiple principles safeguard judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
+          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>PM can remove judges by ordinance</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>President can remove judges on PM advice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>PM can suspend judges</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Added anti-defection law which can involve judicial scrutiny.</t>
+          <t>Removal requires a two-thirds majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Supreme Court’s power of judicial review limits the</t>
+          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>President’s powers</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Parliament’s legislative powers</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Judicial review can check executive actions including PM’s decisions.</t>
+          <t>After the S.P. Gupta case, judicial independence increased.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
+          <t>Which case emphasized the independence of the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Basic Structure Doctrine</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>These principles collectively limit executive control.</t>
+          <t>Known as the Judges’ Transfer case affirming independence.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
+          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Cabinet’s consensus</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Parliament’s decision</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Supreme Court order</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The collegium consists of the CJI and four senior-most judges.</t>
+          <t>Executive follows collegium’s advice.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which case emphasized the independence of the judiciary from the executive?</t>
+          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Yes, thrice</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Known as the Judges’ Transfer case affirming independence.</t>
+          <t>The President can send back recommendations once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who is the custodian of judicial independence in India?</t>
+          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliamentary approval</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Public opinion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CJI safeguards judicial independence.</t>
+          <t>Supreme Court can review executive actions.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
+          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Article 247</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>Judicial Selection Committee</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Judicial Review Board</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Parliament can legislate on judiciary subject under this article.</t>
+          <t>NJAC was declared unconstitutional.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
+          <t>Which article provides for the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cabinet’s consensus</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parliament’s decision</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Supreme Court order</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Executive follows collegium’s advice.</t>
+          <t>It describes the impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which article provides for the removal of Supreme Court judges?</t>
+          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It describes the impeachment process.</t>
+          <t>Collegium protects judicial independence under basic structure.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
+          <t>Which of the following is true about the NJAC?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>It was accepted</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>It replaced the collegium system</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>It empowered PM</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>PM influences appointments by advising the President.</t>
+          <t>It was struck down for undermining judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judicial appointments</t>
+          <t>Who acts as the constitutional head of the judiciary?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Has increased over years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remains constant</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Is absolute</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Collegium limits executive role.</t>
+          <t>CJI is head of judiciary as per convention.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
+          <t>The collegium system was challenged in which case?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>It was added by the 52nd Amendment.</t>
+          <t>The NJAC case questioned collegium’s legitimacy.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
+          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>No involvement</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The Constitution does not specify a time limit.</t>
+          <t>Cabinet advises President on appointments.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Prime Minister’s office can influence judiciary appointments through</t>
+          <t>The PM can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Direct orders</t>
+          <t>Control over Collegium</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Control over Parliament</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Parliamentary resolution</t>
+          <t>Control over Election Commission</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PM influences President through Cabinet advice.</t>
+          <t>President acts on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
+          <t>The removal of a Supreme Court judge requires a</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Simple majority in Parliament</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Judicial Selection Committee</t>
+          <t>Majority in Supreme Court</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Judicial Review Board</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>NJAC was declared unconstitutional.</t>
+          <t>Impeachment requires two-thirds majority in both Houses.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Supreme Court can review actions of the Prime Minister under</t>
+          <t>Who appoints the Registrar General of the Supreme Court?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Article 131</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Article 142</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
+          <t>CJI appoints administrative officers.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
+          <t>Under which Article can a Supreme Court judge be removed?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Executive privilege</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Parliamentary oversight</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Courts check constitutionality of executive actions.</t>
+          <t>It outlines the impeachment procedure.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>The role of the PM in judiciary is</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The President appoints CJI after consultation with senior judges.</t>
+          <t>PM’s role is advisory via President.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who is responsible for the administration of the Supreme Court?</t>
+          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CJI oversees the administration of the Supreme Court.</t>
+          <t>PM advises the President via Cabinet for appointments.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>If unpopular</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>If advised by Parliament</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>If voted by Lok Sabha</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Judiciary ensures constitutional compliance.</t>
+          <t>The President appoints CJI after consultation with senior judges.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
+          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Basic structure of the Constitution</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It was struck down as it compromised judiciary’s independence.</t>
+          <t>It mandates consultation with CJI, Governor, and others.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Prime Minister is accountable to the judiciary in matters of</t>
+          <t>Which body was proposed to replace the collegium system?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Budgetary sanctions</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Foreign policy</t>
+          <t>Supreme Judicial Council</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Election conduct</t>
+          <t>Parliamentary Judicial Panel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Judiciary can review legality of executive acts.</t>
+          <t>NJAC was proposed but struck down by SC.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
+          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>S. P. Gupta Case</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Collegium protects judicial independence under basic structure.</t>
+          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
+          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Initiate impeachment</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Constitutional provisions</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Preside over proceedings</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>These collectively protect judicial independence.</t>
+          <t>The PM may advise the President to initiate proceedings.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The collegium system was challenged in which case?</t>
+          <t>Which article states the conditions for removal of High Court judges?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Article 227</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The NJAC case questioned collegium’s legitimacy.</t>
+          <t>It provides the removal process for High Court judges.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The role of the PM in judiciary is</t>
+          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Article 130</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PM’s role is advisory via President.</t>
+          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
+          <t>What is the role of the Prime Minister in judicial impeachments?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Can impeach judges</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>No formal body</t>
+          <t>Decides final removal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Judicial appointments can be challenged in SC.</t>
+          <t>PM can recommend initiating impeachment proceedings.</t>
         </is>
       </c>
     </row>
@@ -2276,212 +2276,212 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The removal of a Supreme Court judge requires a</t>
+          <t>Which of the following is NOT a feature of the collegium system?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Simple majority in Parliament</t>
+          <t>Confidential recommendations</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Majority in Supreme Court</t>
+          <t>Collegium consists of CJI and senior judges</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>No formal legal backing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Impeachment requires two-thirds majority in both Houses.</t>
+          <t>The executive has no formal role in selection.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
+          <t>Appointment of Attorney General is done by</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI and Governor.</t>
+          <t>President appoints AG on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
+          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>Article 247</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>After the S.P. Gupta case, judicial independence increased.</t>
+          <t>Parliament can legislate on judiciary subject under this article.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
+          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Controlling court procedures</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Appointing judges</t>
+          <t>60 days</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Impeachment of judges</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Judicial independence limits executive interference.</t>
+          <t>The Constitution does not specify a time limit.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
+          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Inefficiency</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>Unpopularity</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>S. R. Bommai</t>
+          <t>Opposition protests</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
+          <t>Judicial review protects Constitution.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who appoints the Lokpal and Lokayuktas?</t>
+          <t>Which body consults the Prime Minister on judicial appointments?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2491,52 +2491,52 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Central Government</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Appointments are made by the President based on recommendations.</t>
+          <t>There is no formal role for PM in collegium consultations.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who is the appointing authority for the Attorney General of India?</t>
+          <t>Who appoints the Lokpal and Lokayuktas?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Central Government</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2546,87 +2546,87 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Appointed by the President on PM’s advice.</t>
+          <t>Appointments are made by the President based on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
+          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI before appointment.</t>
+          <t>PM influences appointments by advising the President.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
+          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>Direct appointment authority</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Consults the Collegium</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The senior-most puisne judge acts as CJI.</t>
+          <t>PM recommends to President but must follow Collegium advice.</t>
         </is>
       </c>
     </row>
@@ -2636,22 +2636,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
+          <t>What role does the PM play in judicial accountability?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Direct appointment authority</t>
+          <t>Can remove judges</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Consults the Collegium</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Direct supervision</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2661,92 +2661,92 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>PM recommends to President but must follow Collegium advice.</t>
+          <t>PM can initiate impeachment recommendation to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
+          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Initiate impeachment</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Preside over proceedings</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>The PM may advise the President to initiate proceedings.</t>
+          <t>Parliament does not participate in appointments.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
+          <t>The Prime Minister’s office can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Inefficiency</t>
+          <t>Direct orders</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Unpopularity</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Opposition protests</t>
+          <t>Parliamentary resolution</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Judicial review protects Constitution.</t>
+          <t>PM influences President through Cabinet advice.</t>
         </is>
       </c>
     </row>
@@ -2756,237 +2756,237 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
+          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Multiple principles safeguard judicial independence.</t>
+          <t>It provides for President’s appointment after consultation.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
+          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only in consultation with Cabinet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Only with President’s approval</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
+          <t>The PM cannot veto; President follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
+          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PM can remove judges by ordinance</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>President can remove judges on PM advice</t>
+          <t>Article 148</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PM can suspend judges</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Removal requires a two-thirds majority in Parliament.</t>
+          <t>It mandates consultation before appointment.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The PM can influence judiciary appointments through</t>
+          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Control over Collegium</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Control over Parliament</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Control over Election Commission</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>President acts on PM’s advice.</t>
+          <t>It tried to curtail judiciary’s power but was struck down.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
+          <t>The PM can recommend removal of a Supreme Court judge under</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Yes, thrice</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>The President can send back recommendations once for reconsideration.</t>
+          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
+          <t>Who acts as the guardian of the independence of the judiciary?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seniority</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Political affiliation</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Executive preference</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Judges are appointed based on merit and integrity.</t>
+          <t>CJI protects judiciary’s independence.</t>
         </is>
       </c>
     </row>
@@ -2996,219 +2996,219 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
+          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Only for Chief Justice</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Only with Parliament approval</t>
+          <t>S. R. Bommai</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Appointments require consultation and collegium recommendations.</t>
+          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The appointment of High Court judges involves consultation with</t>
+          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chief Justice of India only</t>
+          <t>Appointing judges directly</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>State Governor only</t>
+          <t>Forming judiciary</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>Removing judges directly</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Both are consulted for High Court appointments.</t>
+          <t>Judiciary is independent from executive.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>In the impeachment process of a judge, who investigates the charges?</t>
+          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>Basic Structure Doctrine</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>A committee constituted by Parliament investigates.</t>
+          <t>These principles collectively limit executive control.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which of the following is true about the NJAC?</t>
+          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>It was accepted</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>Can override judicial orders</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>It replaced the collegium system</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>It empowered PM</t>
+          <t>Approves court judgments</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>It was struck down for undermining judicial independence.</t>
+          <t>Executive actions including PM’s are subject to judicial review.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
+          <t>In the impeachment process of a judge, who investigates the charges?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Only for High Court appointments</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>The collegium is independent of the executive.</t>
+          <t>A committee constituted by Parliament investigates.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who acts as the constitutional head of the judiciary?</t>
+          <t>Who is responsible for the administration of the Supreme Court?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Chief Justice of India</t>
@@ -3226,767 +3226,767 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CJI is head of judiciary as per convention.</t>
+          <t>CJI oversees the administration of the Supreme Court.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Under which Article can a Supreme Court judge be removed?</t>
+          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>If unpopular</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>If advised by Parliament</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>If voted by Lok Sabha</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>It outlines the impeachment procedure.</t>
+          <t>Judiciary ensures constitutional compliance.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which of the following is true regarding the PM and judiciary?</t>
+          <t>The President can reject collegium recommendations for judicial appointments</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PM can remove judges directly</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PM heads judiciary</t>
+          <t>Multiple times</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PM appoints judges by executive order</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
+          <t>Rejection can be sent back once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
+          <t>Which constitutional article provides immunity to judges from executive interference?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No, never</t>
+          <t>Article 211</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>The President can send recommendations back once on PM’s advice.</t>
+          <t>It mandates separation of judiciary from executive.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
+          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Parliamentary Committee</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 130</t>
+          <t>Union Cabinet</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
+          <t>The Collegium system recommends judges’ appointments.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
+          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 148</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>It mandates consultation before appointment.</t>
+          <t>It was added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who is the final authority in the appointment of High Court judges?</t>
+          <t>The Prime Minister is accountable to the judiciary in matters of</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Budgetary sanctions</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Foreign policy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Election conduct</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Appointment is made by the President after consultation.</t>
+          <t>Judiciary can review legality of executive acts.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The PM’s influence on judiciary appointments has</t>
+          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Increased over time</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Remained constant</t>
+          <t>Three-fourths majority</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Never existed</t>
+          <t>Unanimous approval</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Collegium system reduces direct PM influence.</t>
+          <t>It requires a special majority.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The collegium system is criticized for</t>
+          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Excessive executive control</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Political interference</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Parliamentary involvement</t>
+          <t>Article 311(2)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Its opaque functioning is often criticized.</t>
+          <t>Impeachment procedure is mentioned in Article 124(4).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
+          <t>Who is the appointing authority for the Attorney General of India?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>It mandates consultation with CJI, Governor, and others.</t>
+          <t>Appointed by the President on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
+          <t>Which landmark case established the Collegium system?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Appointing judges directly</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Forming judiciary</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Removing judges directly</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Judiciary is independent from executive.</t>
+          <t>It reinforced judiciary’s primacy in appointments.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
+          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S. P. Gupta Case</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>Constitutional provisions</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
+          <t>These collectively protect judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The President can reject collegium recommendations for judicial appointments</t>
+          <t>The Prime Minister’s influence on judicial appointments</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Multiple times</t>
+          <t>Has increased over years</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Remains constant</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Is absolute</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Rejection can be sent back once for reconsideration.</t>
+          <t>Collegium limits executive role.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
+          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parliamentary Committee</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Union Cabinet</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>The Collegium system recommends judges’ appointments.</t>
+          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about the collegium system?</t>
+          <t>Who is the custodian of judicial independence in India?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>It consists of the CJI and four senior judges</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>It was created by a Supreme Court judgment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>It recommends appointments of judges</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>The PM is not part of the collegium.</t>
+          <t>CJI safeguards judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which body consults the Prime Minister on judicial appointments?</t>
+          <t>Which body nominates the members of the collegium?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>There is no formal role for PM in collegium consultations.</t>
+          <t>Collegium is composed of judges only.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
+          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Seniority</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Three-fourths majority</t>
+          <t>Political affiliation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Unanimous approval</t>
+          <t>Executive preference</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>It requires a special majority.</t>
+          <t>Judges are appointed based on merit and integrity.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who acts as the guardian of the independence of the judiciary?</t>
+          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>CJI protects judiciary’s independence.</t>
+          <t>It requires consultation with CJI before appointment.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Prime Minister directly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Only for Chief Justice</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Only with Parliament approval</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>The President appoints AG following PM’s advice.</t>
+          <t>Appointments require consultation and collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The principle of separation of powers implies the PM should</t>
+          <t>Which of the following is NOT true about the collegium system?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Directly control judiciary</t>
+          <t>It consists of the CJI and four senior judges</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Influence judiciary indirectly</t>
+          <t>It was created by a Supreme Court judgment</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Appoint judges directly</t>
+          <t>It recommends appointments of judges</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Separation mandates judicial independence.</t>
+          <t>The PM is not part of the collegium.</t>
         </is>
       </c>
     </row>
@@ -4032,106 +4032,106 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Appointment of Attorney General is done by</t>
+          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Collegium</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Parliament</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>President appoints AG on PM’s advice.</t>
+          <t>But President acts on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
+          <t>The principle of separation of powers implies the PM should</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Directly control judiciary</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Influence judiciary indirectly</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Appoint judges directly</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>It tried to curtail judiciary’s power but was struck down.</t>
+          <t>Separation mandates judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
+          <t>The appointment of High Court judges involves consultation with</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Chief Justice of India only</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>State Governor only</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4141,237 +4141,237 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Parliament does not participate in appointments.</t>
+          <t>Both are consulted for High Court appointments.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
+          <t>The Supreme Court can review actions of the Prime Minister under</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Article 131</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 142</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The NJAC was struck down for violating judicial independence.</t>
+          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
+          <t>Which of the following is true regarding the PM and judiciary?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>PM can remove judges directly</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Can override judicial orders</t>
+          <t>PM heads judiciary</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Approves court judgments</t>
+          <t>PM appoints judges by executive order</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Executive actions including PM’s are subject to judicial review.</t>
+          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The PM’s role in judicial appointments is</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Decisive</t>
+          <t>Prime Minister directly</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Constitutionally mandated</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Non-existent</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>PM advises President but actual appointment is collegium-based.</t>
+          <t>The President appoints AG following PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which body was proposed to replace the collegium system?</t>
+          <t>Which article protects judges from arbitrary removal by the executive?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Supreme Judicial Council</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Parliamentary Judicial Panel</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>NJAC was proposed but struck down by SC.</t>
+          <t>Separation of judiciary from executive ensures protection.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which body nominates the members of the collegium?</t>
+          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Senior-most judge</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Supreme Court itself</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Collegium is composed of judges only.</t>
+          <t>The senior-most puisne judge acts as CJI.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
+          <t>The President appoints Supreme Court judges after consultation with</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4381,92 +4381,92 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>But President acts on collegium recommendations.</t>
+          <t>Consultation is constitutionally mandated.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
+          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>No, never</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 311(2)</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Impeachment procedure is mentioned in Article 124(4).</t>
+          <t>The President can send recommendations back once on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
+          <t>The Supreme Court’s power of judicial review limits the</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>President’s powers</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Parliament’s legislative powers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>PM advises the President via Cabinet for appointments.</t>
+          <t>Judicial review can check executive actions including PM’s decisions.</t>
         </is>
       </c>
     </row>

--- a/Data/IPJudicialSystem.xlsx
+++ b/Data/IPJudicialSystem.xlsx
@@ -472,251 +472,251 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
+          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The NJAC was struck down for violating judicial independence.</t>
+          <t>It requires consultation with CJI before appointment.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
+          <t>The PM’s influence on judiciary appointments has</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Increased over time</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Remained constant</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Never existed</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI and Governor.</t>
+          <t>Collegium system reduces direct PM influence.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
+          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Initiate impeachment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No formal body</t>
+          <t>Preside over proceedings</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Judicial appointments can be challenged in SC.</t>
+          <t>The PM may advise the President to initiate proceedings.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
+          <t>Who appoints the Registrar General of the Supreme Court?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Basic structure of the Constitution</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>It was struck down as it compromised judiciary’s independence.</t>
+          <t>CJI appoints administrative officers.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
+          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Executive privilege</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Parliamentary oversight</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Courts check constitutionality of executive actions.</t>
+          <t>It provides for President’s appointment after consultation.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The PM’s influence on judiciary appointments has</t>
+          <t>The collegium system was challenged in which case?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Increased over time</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Remained constant</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Never existed</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Collegium system reduces direct PM influence.</t>
+          <t>The NJAC case questioned collegium’s legitimacy.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -726,14 +726,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Chief Justice of India</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Parliament</t>
@@ -741,612 +741,612 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>On the advice of the PM.</t>
+          <t>Parliament does not participate in appointments.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
+          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Can override judicial orders</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Only for High Court appointments</t>
+          <t>Approves court judgments</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The collegium is independent of the executive.</t>
+          <t>Executive actions including PM’s are subject to judicial review.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
+          <t>The Prime Minister’s influence on judicial appointments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Controlling court procedures</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Appointing judges</t>
+          <t>Has increased over years</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Impeachment of judges</t>
+          <t>Remains constant</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Is absolute</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Judicial independence limits executive interference.</t>
+          <t>Collegium limits executive role.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The PM’s role in judicial appointments is</t>
+          <t>The role of the PM in judiciary is</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Decisive</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Constitutionally mandated</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Non-existent</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PM advises President but actual appointment is collegium-based.</t>
+          <t>PM’s role is advisory via President.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The collegium system is criticized for</t>
+          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Parliamentary Committee</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Excessive executive control</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Political interference</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Parliamentary involvement</t>
+          <t>Union Cabinet</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Its opaque functioning is often criticized.</t>
+          <t>The Collegium system recommends judges’ appointments.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
+          <t>Which case emphasized the independence of the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Always approved</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Never questioned</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Controlled by legislature</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Judiciary can invalidate unconstitutional executive actions.</t>
+          <t>Known as the Judges’ Transfer case affirming independence.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The collegium consists of the CJI and four senior-most judges.</t>
+          <t>The President appoints CJI after consultation with senior judges.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who is the final authority in the appointment of High Court judges?</t>
+          <t>The Prime Minister’s office can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Direct orders</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Parliamentary resolution</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Appointment is made by the President after consultation.</t>
+          <t>PM influences President through Cabinet advice.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
+          <t>Who is responsible for the administration of the Supreme Court?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Judicial appointments</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>It upheld the collegium system against NJAC.</t>
+          <t>CJI oversees the administration of the Supreme Court.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
+          <t>The PM can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Control over Collegium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Control over Parliament</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Control over Election Commission</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Added anti-defection law which can involve judicial scrutiny.</t>
+          <t>President acts on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who has the final say in appointment of Supreme Court judges?</t>
+          <t>Which landmark case established the Collegium system?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>President appoints judges but follows collegium recommendations.</t>
+          <t>It reinforced judiciary’s primacy in appointments.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
+          <t>Which of the following is NOT a feature of the collegium system?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Confidential recommendations</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Collegium consists of CJI and senior judges</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No formal legal backing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Multiple principles safeguard judicial independence.</t>
+          <t>The executive has no formal role in selection.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
+          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PM can remove judges by ordinance</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>If unpopular</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>President can remove judges on PM advice</t>
+          <t>If advised by Parliament</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PM can suspend judges</t>
+          <t>If voted by Lok Sabha</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Removal requires a two-thirds majority in Parliament.</t>
+          <t>Judiciary ensures constitutional compliance.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
+          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>After the S.P. Gupta case, judicial independence increased.</t>
+          <t>Added anti-defection law which can involve judicial scrutiny.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which case emphasized the independence of the judiciary from the executive?</t>
+          <t>Which of the following is true regarding the PM and judiciary?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>PM can remove judges directly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>PM heads judiciary</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>PM appoints judges by executive order</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Known as the Judges’ Transfer case affirming independence.</t>
+          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
+          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cabinet’s consensus</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Parliament’s decision</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Supreme Court order</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Executive follows collegium’s advice.</t>
+          <t>The NJAC was struck down for violating judicial independence.</t>
         </is>
       </c>
     </row>
@@ -1356,29 +1356,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
+          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Yes, always</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No, never</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Yes, once</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Yes, twice</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Yes, thrice</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Yes, once</t>
@@ -1386,127 +1386,127 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The President can send back recommendations once for reconsideration.</t>
+          <t>The President can send recommendations back once on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
+          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Parliamentary approval</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Public opinion</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Supreme Court can review executive actions.</t>
+          <t>PM advises the President via Cabinet for appointments.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
+          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Judicial Selection Committee</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Judicial Review Board</t>
+          <t>Article 130</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>NJAC was declared unconstitutional.</t>
+          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which article provides for the removal of Supreme Court judges?</t>
+          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>S. P. Gupta Case</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>It describes the impeachment process.</t>
+          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
         </is>
       </c>
     </row>
@@ -1516,197 +1516,197 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
+          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>60 days</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Collegium protects judicial independence under basic structure.</t>
+          <t>The Constitution does not specify a time limit.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which of the following is true about the NJAC?</t>
+          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>It was accepted</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>It replaced the collegium system</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>It empowered PM</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It was struck down for undermining judicial independence.</t>
+          <t>Collegium protects judicial independence under basic structure.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who acts as the constitutional head of the judiciary?</t>
+          <t>Which constitutional article provides immunity to judges from executive interference?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 211</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CJI is head of judiciary as per convention.</t>
+          <t>It mandates separation of judiciary from executive.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The collegium system was challenged in which case?</t>
+          <t>Who is the final authority in the appointment of High Court judges?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>The NJAC case questioned collegium’s legitimacy.</t>
+          <t>Appointment is made by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
+          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Consultation</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Only in consultation with Cabinet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No involvement</t>
+          <t>Only with President’s approval</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cabinet advises President on appointments.</t>
+          <t>The PM cannot veto; President follows collegium recommendations.</t>
         </is>
       </c>
     </row>
@@ -1716,87 +1716,87 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The PM can influence judiciary appointments through</t>
+          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>Controlling court procedures</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Control over Collegium</t>
+          <t>Appointing judges</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Control over Parliament</t>
+          <t>Impeachment of judges</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Control over Election Commission</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>President acts on PM’s advice.</t>
+          <t>Judicial independence limits executive interference.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The removal of a Supreme Court judge requires a</t>
+          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Simple majority in Parliament</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Majority in Supreme Court</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Impeachment requires two-thirds majority in both Houses.</t>
+          <t>It tried to curtail judiciary’s power but was struck down.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who appoints the Registrar General of the Supreme Court?</t>
+          <t>The President appoints Supreme Court judges after consultation with</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1821,352 +1821,352 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CJI appoints administrative officers.</t>
+          <t>Consultation is constitutionally mandated.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Under which Article can a Supreme Court judge be removed?</t>
+          <t>The Prime Minister is accountable to the judiciary in matters of</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Budgetary sanctions</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Foreign policy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Election conduct</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>It outlines the impeachment procedure.</t>
+          <t>Judiciary can review legality of executive acts.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The role of the PM in judiciary is</t>
+          <t>What role does the PM play in judicial accountability?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>Can remove judges</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Direct supervision</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PM’s role is advisory via President.</t>
+          <t>PM can initiate impeachment recommendation to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
+          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Three-fourths majority</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>Unanimous approval</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>PM advises the President via Cabinet for appointments.</t>
+          <t>It requires a special majority.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>The PM’s role in judicial appointments is</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Decisive</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Constitutionally mandated</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Non-existent</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The President appoints CJI after consultation with senior judges.</t>
+          <t>PM advises President but actual appointment is collegium-based.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
+          <t>The Supreme Court can review actions of the Prime Minister under</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Article 131</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Article 142</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>It mandates consultation with CJI, Governor, and others.</t>
+          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which body was proposed to replace the collegium system?</t>
+          <t>Which of the following is NOT true about the collegium system?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>It consists of the CJI and four senior judges</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>It was created by a Supreme Court judgment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Supreme Judicial Council</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Parliamentary Judicial Panel</t>
+          <t>It recommends appointments of judges</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NJAC was proposed but struck down by SC.</t>
+          <t>The PM is not part of the collegium.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
+          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S. P. Gupta Case</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>Lok Sabha members</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
+          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
+          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Initiate impeachment</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preside over proceedings</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The PM may advise the President to initiate proceedings.</t>
+          <t>PM influences appointments by advising the President.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which article states the conditions for removal of High Court judges?</t>
+          <t>Which article protects judges from arbitrary removal by the executive?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2176,312 +2176,312 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Article 227</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>It provides the removal process for High Court judges.</t>
+          <t>Separation of judiciary from executive ensures protection.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
+          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Inefficiency</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Unpopularity</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Article 130</t>
+          <t>Opposition protests</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
+          <t>Judicial review protects Constitution.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in judicial impeachments?</t>
+          <t>Which of the following is true about the NJAC?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Can impeach judges</t>
+          <t>It was accepted</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>It replaced the collegium system</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Decides final removal</t>
+          <t>It empowered PM</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PM can recommend initiating impeachment proceedings.</t>
+          <t>It was struck down for undermining judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a feature of the collegium system?</t>
+          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Confidential recommendations</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Collegium consists of CJI and senior judges</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>No formal legal backing</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The executive has no formal role in selection.</t>
+          <t>It mandates consultation with CJI, Governor, and others.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Appointment of Attorney General is done by</t>
+          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>President appoints AG on PM’s advice.</t>
+          <t>It requires consultation with CJI and Governor.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
+          <t>The Supreme Court’s power of judicial review limits the</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 247</t>
+          <t>President’s powers</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>Parliament’s legislative powers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Parliament can legislate on judiciary subject under this article.</t>
+          <t>Judicial review can check executive actions including PM’s decisions.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
+          <t>Which article provides for the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>The Constitution does not specify a time limit.</t>
+          <t>It describes the impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
+          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Inefficiency</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unpopularity</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Opposition protests</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Judicial review protects Constitution.</t>
+          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which body consults the Prime Minister on judicial appointments?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2491,437 +2491,437 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>There is no formal role for PM in collegium consultations.</t>
+          <t>On the advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who appoints the Lokpal and Lokayuktas?</t>
+          <t>What is the role of the Prime Minister in judicial impeachments?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Can impeach judges</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Central Government</t>
+          <t>Decides final removal</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Appointments are made by the President based on recommendations.</t>
+          <t>PM can recommend initiating impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
+          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>Judicial Selection Committee</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Judicial Review Board</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>PM influences appointments by advising the President.</t>
+          <t>NJAC was declared unconstitutional.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
+          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Direct appointment authority</t>
+          <t>Judicial appointments</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Consults the Collegium</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>PM recommends to President but must follow Collegium advice.</t>
+          <t>It upheld the collegium system against NJAC.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What role does the PM play in judicial accountability?</t>
+          <t>Who appoints the Lokpal and Lokayuktas?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Can remove judges</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Direct supervision</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Central Government</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>PM can initiate impeachment recommendation to Parliament.</t>
+          <t>Appointments are made by the President based on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
+          <t>Who acts as the constitutional head of the judiciary?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Chief Justice of India</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Parliament does not participate in appointments.</t>
+          <t>CJI is head of judiciary as per convention.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Prime Minister’s office can influence judiciary appointments through</t>
+          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct orders</t>
+          <t>Executive privilege</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Parliamentary oversight</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Parliamentary resolution</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>PM influences President through Cabinet advice.</t>
+          <t>Courts check constitutionality of executive actions.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
+          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Cabinet’s consensus</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Parliament’s decision</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Supreme Court order</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>It provides for President’s appointment after consultation.</t>
+          <t>Executive follows collegium’s advice.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
+          <t>Which body nominates the members of the collegium?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Only in consultation with Cabinet</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Only with President’s approval</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The PM cannot veto; President follows collegium recommendations.</t>
+          <t>Collegium is composed of judges only.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
+          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>PM can remove judges by ordinance</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Article 148</t>
+          <t>President can remove judges on PM advice</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>PM can suspend judges</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>It mandates consultation before appointment.</t>
+          <t>Removal requires a two-thirds majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
+          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>It tried to curtail judiciary’s power but was struck down.</t>
+          <t>After the S.P. Gupta case, judicial independence increased.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The PM can recommend removal of a Supreme Court judge under</t>
+          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2931,127 +2931,127 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Article 311</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Article 311(2)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>Article 124(4)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Article 356</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Article 124(4)</t>
-        </is>
-      </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
+          <t>Impeachment procedure is mentioned in Article 124(4).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who acts as the guardian of the independence of the judiciary?</t>
+          <t>The appointment of High Court judges involves consultation with</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India only</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>State Governor only</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CJI protects judiciary’s independence.</t>
+          <t>Both are consulted for High Court appointments.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
+          <t>Which body consults the Prime Minister on judicial appointments?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Golak Nath</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>S. R. Bommai</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
+          <t>There is no formal role for PM in collegium consultations.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
+          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Appointing judges directly</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Forming judiciary</t>
+          <t>Constitutional provisions</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Removing judges directly</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3066,32 +3066,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Judiciary is independent from executive.</t>
+          <t>These collectively protect judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
+          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Appointing judges directly</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Basic Structure Doctrine</t>
+          <t>Forming judiciary</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>Removing judges directly</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3106,207 +3106,207 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>These principles collectively limit executive control.</t>
+          <t>Judiciary is independent from executive.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
+          <t>The President can reject collegium recommendations for judicial appointments</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Can override judicial orders</t>
+          <t>Multiple times</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Approves court judgments</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Executive actions including PM’s are subject to judicial review.</t>
+          <t>Rejection can be sent back once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>In the impeachment process of a judge, who investigates the charges?</t>
+          <t>Which body was proposed to replace the collegium system?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Supreme Judicial Council</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliamentary Judicial Panel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>A committee constituted by Parliament investigates.</t>
+          <t>NJAC was proposed but struck down by SC.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who is responsible for the administration of the Supreme Court?</t>
+          <t>The removal of a Supreme Court judge requires a</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Simple majority in Parliament</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Majority in Supreme Court</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CJI oversees the administration of the Supreme Court.</t>
+          <t>Impeachment requires two-thirds majority in both Houses.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
+          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>If unpopular</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>If advised by Parliament</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>If voted by Lok Sabha</t>
+          <t>No formal body</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Judiciary ensures constitutional compliance.</t>
+          <t>Judicial appointments can be challenged in SC.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The President can reject collegium recommendations for judicial appointments</t>
+          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Multiple times</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Only for High Court appointments</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Rejection can be sent back once for reconsideration.</t>
+          <t>The collegium is independent of the executive.</t>
         </is>
       </c>
     </row>
@@ -3316,259 +3316,259 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which constitutional article provides immunity to judges from executive interference?</t>
+          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Always approved</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Article 211</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Never questioned</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Controlled by legislature</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>It mandates separation of judiciary from executive.</t>
+          <t>Judiciary can invalidate unconstitutional executive actions.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
+          <t>Under which Article can a Supreme Court judge be removed?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Parliamentary Committee</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Union Cabinet</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The Collegium system recommends judges’ appointments.</t>
+          <t>It outlines the impeachment procedure.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
+          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>It was added by the 52nd Amendment.</t>
+          <t>But President acts on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Prime Minister is accountable to the judiciary in matters of</t>
+          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Budgetary sanctions</t>
+          <t>Article 247</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Foreign policy</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Election conduct</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Judiciary can review legality of executive acts.</t>
+          <t>Parliament can legislate on judiciary subject under this article.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
+          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Three-fourths majority</t>
+          <t>Only for Chief Justice</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Unanimous approval</t>
+          <t>Only with Parliament approval</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>It requires a special majority.</t>
+          <t>Appointments require consultation and collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
+          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Direct appointment authority</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Consults the Collegium</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 311(2)</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Impeachment procedure is mentioned in Article 124(4).</t>
+          <t>PM recommends to President but must follow Collegium advice.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Who is the appointing authority for the Attorney General of India?</t>
+          <t>Appointment of Attorney General is done by</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Chief Justice of India</t>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Appointed by the President on PM’s advice.</t>
+          <t>President appoints AG on PM’s advice.</t>
         </is>
       </c>
     </row>
@@ -3596,64 +3596,64 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which landmark case established the Collegium system?</t>
+          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Basic structure of the Constitution</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It reinforced judiciary’s primacy in appointments.</t>
+          <t>It was struck down as it compromised judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
+          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Judicial review</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Basic structure doctrine</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Constitutional provisions</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Judicial review</t>
-        </is>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>All of the above</t>
@@ -3666,109 +3666,109 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>These collectively protect judicial independence.</t>
+          <t>Multiple principles safeguard judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judicial appointments</t>
+          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Has increased over years</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Remains constant</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Is absolute</t>
+          <t>Yes, thrice</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Collegium limits executive role.</t>
+          <t>The President can send back recommendations once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
+          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 148</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Any member of Parliament</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
+          <t>It mandates consultation before appointment.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who is the custodian of judicial independence in India?</t>
+          <t>Who acts as the guardian of the independence of the judiciary?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Chief Justice of India</t>
@@ -3786,127 +3786,127 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CJI safeguards judicial independence.</t>
+          <t>CJI protects judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which body nominates the members of the collegium?</t>
+          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>No involvement</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Collegium is composed of judges only.</t>
+          <t>Cabinet advises President on appointments.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seniority</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Prime Minister directly</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Political affiliation</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Executive preference</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Judges are appointed based on merit and integrity.</t>
+          <t>The President appoints AG following PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
+          <t>The collegium system is criticized for</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Excessive executive control</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Political interference</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Parliamentary involvement</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI before appointment.</t>
+          <t>Its opaque functioning is often criticized.</t>
         </is>
       </c>
     </row>
@@ -3916,92 +3916,92 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
+          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Only for Chief Justice</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Only with Parliament approval</t>
+          <t>S. R. Bommai</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Appointments require consultation and collegium recommendations.</t>
+          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about the collegium system?</t>
+          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>It consists of the CJI and four senior judges</t>
+          <t>Seniority</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>It was created by a Supreme Court judgment</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Political affiliation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>It recommends appointments of judges</t>
+          <t>Executive preference</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>The PM is not part of the collegium.</t>
+          <t>Judges are appointed based on merit and integrity.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
+          <t>Who has the final say in appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4011,14 +4011,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>Collegium</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Election Commission</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>President</t>
@@ -4026,227 +4026,227 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
+          <t>President appoints judges but follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
+          <t>Which article states the conditions for removal of High Court judges?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 227</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>But President acts on collegium recommendations.</t>
+          <t>It provides the removal process for High Court judges.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The principle of separation of powers implies the PM should</t>
+          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Directly control judiciary</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Influence judiciary indirectly</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Appoint judges directly</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Separation mandates judicial independence.</t>
+          <t>The senior-most puisne judge acts as CJI.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The appointment of High Court judges involves consultation with</t>
+          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chief Justice of India only</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>State Governor only</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Both are consulted for High Court appointments.</t>
+          <t>The collegium consists of the CJI and four senior-most judges.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Supreme Court can review actions of the Prime Minister under</t>
+          <t>In the impeachment process of a judge, who investigates the charges?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Article 131</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Article 142</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
+          <t>A committee constituted by Parliament investigates.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which of the following is true regarding the PM and judiciary?</t>
+          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PM can remove judges directly</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PM heads judiciary</t>
+          <t>Basic Structure Doctrine</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PM appoints judges by executive order</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
+          <t>These principles collectively limit executive control.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Who is the custodian of judicial independence in India?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Prime Minister directly</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4256,177 +4256,177 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>The President appoints AG following PM’s advice.</t>
+          <t>CJI safeguards judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which article protects judges from arbitrary removal by the executive?</t>
+          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Parliamentary approval</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Public opinion</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive ensures protection.</t>
+          <t>Supreme Court can review executive actions.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
+          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>The senior-most puisne judge acts as CJI.</t>
+          <t>It was added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The President appoints Supreme Court judges after consultation with</t>
+          <t>The PM can recommend removal of a Supreme Court judge under</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Consultation is constitutionally mandated.</t>
+          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
+          <t>The principle of separation of powers implies the PM should</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Directly control judiciary</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>No, never</t>
+          <t>Influence judiciary indirectly</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Appoint judges directly</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>The President can send recommendations back once on PM’s advice.</t>
+          <t>Separation mandates judicial independence.</t>
         </is>
       </c>
     </row>
@@ -4436,37 +4436,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Supreme Court’s power of judicial review limits the</t>
+          <t>Who is the appointing authority for the Attorney General of India?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>President’s powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Parliament’s legislative powers</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Judicial review can check executive actions including PM’s decisions.</t>
+          <t>Appointed by the President on PM’s advice.</t>
         </is>
       </c>
     </row>

--- a/Data/IPJudicialSystem.xlsx
+++ b/Data/IPJudicialSystem.xlsx
@@ -472,581 +472,581 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
+          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Senior-most judge</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI before appointment.</t>
+          <t>The senior-most puisne judge acts as CJI.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The PM’s influence on judiciary appointments has</t>
+          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Increased over time</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Remained constant</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Never existed</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Reduced over time</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Collegium system reduces direct PM influence.</t>
+          <t>The collegium consists of the CJI and four senior-most judges.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
+          <t>In the impeachment process of a judge, who investigates the charges?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Initiate impeachment</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Preside over proceedings</t>
+          <t>President</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Recommend removal</t>
+          <t>Parliamentary committee</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The PM may advise the President to initiate proceedings.</t>
+          <t>A committee constituted by Parliament investigates.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Who appoints the Registrar General of the Supreme Court?</t>
+          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of Powers</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Basic Structure Doctrine</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial Review</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CJI appoints administrative officers.</t>
+          <t>These principles collectively limit executive control.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
+          <t>Who is the custodian of judicial independence in India?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>It provides for President’s appointment after consultation.</t>
+          <t>CJI safeguards judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The collegium system was challenged in which case?</t>
+          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Parliamentary approval</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Public opinion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The NJAC case questioned collegium’s legitimacy.</t>
+          <t>Supreme Court can review executive actions.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
+          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>42nd</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>44th</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>61st</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>52nd</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Parliament does not participate in appointments.</t>
+          <t>It was added by the 52nd Amendment.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
+          <t>The PM can recommend removal of a Supreme Court judge under</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Can override judicial orders</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Approves court judgments</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Subject to judicial orders</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Executive actions including PM’s are subject to judicial review.</t>
+          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judicial appointments</t>
+          <t>The principle of separation of powers implies the PM should</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Directly control judiciary</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Has increased over years</t>
+          <t>Influence judiciary indirectly</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Remains constant</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Is absolute</t>
+          <t>Appoint judges directly</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Has reduced after collegium system</t>
+          <t>Not interfere in judiciary</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Collegium limits executive role.</t>
+          <t>Separation mandates judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The role of the PM in judiciary is</t>
+          <t>Who is the appointing authority for the Attorney General of India?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Legislative</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Judicial</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Advisory</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>PM’s role is advisory via President.</t>
+          <t>Appointed by the President on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
+          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Parliamentary Committee</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Union Cabinet</t>
+          <t>Yes, thrice</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The Collegium system recommends judges’ appointments.</t>
+          <t>The President can send back recommendations once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which case emphasized the independence of the judiciary from the executive?</t>
+          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>Article 148</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>S.P. Gupta v. Union of India</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Known as the Judges’ Transfer case affirming independence.</t>
+          <t>It mandates consultation before appointment.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who appoints the Chief Justice of India?</t>
+          <t>Who acts as the guardian of the independence of the judiciary?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The President appoints CJI after consultation with senior judges.</t>
+          <t>CJI protects judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Prime Minister’s office can influence judiciary appointments through</t>
+          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Consultation</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Direct orders</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Parliamentary resolution</t>
+          <t>No involvement</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cabinet advice to President</t>
+          <t>Recommendation to President</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PM influences President through Cabinet advice.</t>
+          <t>Cabinet advises President on appointments.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who is responsible for the administration of the Supreme Court?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister directly</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>President on PM’s advice</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CJI oversees the administration of the Supreme Court.</t>
+          <t>The President appoints AG following PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The PM can influence judiciary appointments through</t>
+          <t>The collegium system is criticized for</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Control over Collegium</t>
+          <t>Excessive executive control</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Control over Parliament</t>
+          <t>Political interference</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Control over Election Commission</t>
+          <t>Parliamentary involvement</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Control over President</t>
+          <t>Lack of transparency</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>President acts on PM’s advice.</t>
+          <t>Its opaque functioning is often criticized.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which landmark case established the Collegium system?</t>
+          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1126,957 +1126,957 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Golak Nath</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Minerva Mills</t>
+          <t>S. R. Bommai</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>S. P. Gupta v. Union of India</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>It reinforced judiciary’s primacy in appointments.</t>
+          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following is NOT a feature of the collegium system?</t>
+          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Seniority</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Confidential recommendations</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Collegium consists of CJI and senior judges</t>
+          <t>Political affiliation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>No formal legal backing</t>
+          <t>Executive preference</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Executive involvement in selection</t>
+          <t>Merit</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The executive has no formal role in selection.</t>
+          <t>Judges are appointed based on merit and integrity.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
+          <t>Who has the final say in appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>If unpopular</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>If advised by Parliament</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>If voted by Lok Sabha</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>If unconstitutional</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Judiciary ensures constitutional compliance.</t>
+          <t>President appoints judges but follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
+          <t>Which article states the conditions for removal of High Court judges?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Article 227</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Article 217(1)(b)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Added anti-defection law which can involve judicial scrutiny.</t>
+          <t>It provides the removal process for High Court judges.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which of the following is true regarding the PM and judiciary?</t>
+          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PM can remove judges directly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PM heads judiciary</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>Sometimes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PM appoints judges by executive order</t>
+          <t>Only for High Court appointments</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PM’s role is limited to advising President on appointments</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
+          <t>The collegium is independent of the executive.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
+          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S.P. Gupta case</t>
+          <t>Always approved</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Minerva Mills case</t>
+          <t>Never questioned</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Controlled by legislature</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NJAC case</t>
+          <t>Subject to judicial scrutiny</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The NJAC was struck down for violating judicial independence.</t>
+          <t>Judiciary can invalidate unconstitutional executive actions.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
+          <t>Under which Article can a Supreme Court judge be removed?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>No, never</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The President can send recommendations back once on PM’s advice.</t>
+          <t>It outlines the impeachment procedure.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
+          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cabinet recommendation to the President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>PM advises the President via Cabinet for appointments.</t>
+          <t>But President acts on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
+          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Article 247</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Article 312</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Article 130</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Article 246</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
+          <t>Parliament can legislate on judiciary subject under this article.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
+          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S. P. Gupta Case</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Indira Gandhi v. Raj Narain</t>
+          <t>Only for Chief Justice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>Only with Parliament approval</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
+          <t>Appointments require consultation and collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
+          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>Direct appointment authority</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>Consults the Collegium</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No fixed time</t>
+          <t>Recommends to President</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The Constitution does not specify a time limit.</t>
+          <t>PM recommends to President but must follow Collegium advice.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
+          <t>Appointment of Attorney General is done by</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Collegium protects judicial independence under basic structure.</t>
+          <t>President appoints AG on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which constitutional article provides immunity to judges from executive interference?</t>
+          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Article 211</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Basic structure of the Constitution</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>It mandates separation of judiciary from executive.</t>
+          <t>It was struck down as it compromised judiciary’s independence.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who is the final authority in the appointment of High Court judges?</t>
+          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Appointment is made by the President after consultation.</t>
+          <t>Multiple principles safeguard judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
+          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Only in consultation with Cabinet</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Only with President’s approval</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The PM cannot veto; President follows collegium recommendations.</t>
+          <t>After the S.P. Gupta case, judicial independence increased.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
+          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Controlling court procedures</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Appointing judges</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Impeachment of judges</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 311(2)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Judicial independence limits executive interference.</t>
+          <t>Impeachment procedure is mentioned in Article 124(4).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
+          <t>The appointment of High Court judges involves consultation with</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Chief Justice of India only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>State Governor only</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61st Amendment</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Chief Justice of India and State Governor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>It tried to curtail judiciary’s power but was struck down.</t>
+          <t>Both are consulted for High Court appointments.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The President appoints Supreme Court judges after consultation with</t>
+          <t>Which body consults the Prime Minister on judicial appointments?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chief Justice of India and senior judges</t>
+          <t>No formal consultation</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Consultation is constitutionally mandated.</t>
+          <t>There is no formal role for PM in collegium consultations.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Prime Minister is accountable to the judiciary in matters of</t>
+          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Budgetary sanctions</t>
+          <t>Constitutional provisions</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Foreign policy</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Election conduct</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Legality of actions</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Judiciary can review legality of executive acts.</t>
+          <t>These collectively protect judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What role does the PM play in judicial accountability?</t>
+          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Can remove judges</t>
+          <t>Appointing judges directly</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>Forming judiciary</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Direct supervision</t>
+          <t>Removing judges directly</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Recommends impeachment</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PM can initiate impeachment recommendation to Parliament.</t>
+          <t>Judiciary is independent from executive.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
+          <t>The President can reject collegium recommendations for judicial appointments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>Multiple times</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Three-fourths majority</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Unanimous approval</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Two-thirds majority</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>It requires a special majority.</t>
+          <t>Rejection can be sent back once for reconsideration.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The PM’s role in judicial appointments is</t>
+          <t>Which body was proposed to replace the collegium system?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Decisive</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Constitutionally mandated</t>
+          <t>Supreme Judicial Council</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Non-existent</t>
+          <t>Parliamentary Judicial Panel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nominal</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PM advises President but actual appointment is collegium-based.</t>
+          <t>NJAC was proposed but struck down by SC.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Supreme Court can review actions of the Prime Minister under</t>
+          <t>The removal of a Supreme Court judge requires a</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Article 131</t>
+          <t>Simple majority in Parliament</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Article 142</t>
+          <t>Majority in Supreme Court</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Presidential order</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Article 32</t>
+          <t>Special majority in Parliament</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
+          <t>Impeachment requires two-thirds majority in both Houses.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which of the following is NOT true about the collegium system?</t>
+          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>It consists of the CJI and four senior judges</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>It was created by a Supreme Court judgment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>It recommends appointments of judges</t>
+          <t>No formal body</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>It involves the Prime Minister directly</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The PM is not part of the collegium.</t>
+          <t>Judicial appointments can be challenged in SC.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
+          <t>Who appoints the Attorney General of India?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2086,397 +2086,397 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lok Sabha members</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Chief Justice of India</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Any member of Parliament</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Any member of Parliament</t>
-        </is>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
+          <t>On the advice of the PM.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
+          <t>What is the role of the Prime Minister in judicial impeachments?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>Can impeach judges</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direct appointment</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Parliament approval</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Judicial Commission</t>
+          <t>Decides final removal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Presidential advice</t>
+          <t>Recommends removal to the President</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PM influences appointments by advising the President.</t>
+          <t>PM can recommend initiating impeachment proceedings.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which article protects judges from arbitrary removal by the executive?</t>
+          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Judicial Appointment Commission</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Judicial Selection Committee</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>Judicial Review Board</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 50</t>
+          <t>National Judicial Appointments Commission</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Separation of judiciary from executive ensures protection.</t>
+          <t>NJAC was declared unconstitutional.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
+          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Judicial appointments</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Inefficiency</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unpopularity</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Opposition protests</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unconstitutionality</t>
+          <t>Collegium system</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Judicial review protects Constitution.</t>
+          <t>It upheld the collegium system against NJAC.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which of the following is true about the NJAC?</t>
+          <t>Who appoints the Lokpal and Lokayuktas?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>It was accepted</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>It replaced the collegium system</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>It empowered PM</t>
+          <t>Central Government</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>It was rejected by Supreme Court</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>It was struck down for undermining judicial independence.</t>
+          <t>Appointments are made by the President based on recommendations.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
+          <t>Who acts as the constitutional head of the judiciary?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Article 222</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Article 230</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>It mandates consultation with CJI, Governor, and others.</t>
+          <t>CJI is head of judiciary as per convention.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
+          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Executive privilege</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Parliamentary oversight</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Federalism</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Judicial review</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>It requires consultation with CJI and Governor.</t>
+          <t>Courts check constitutionality of executive actions.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Supreme Court’s power of judicial review limits the</t>
+          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>Cabinet’s consensus</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>President’s powers</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Parliament’s legislative powers</t>
+          <t>Parliament’s decision</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>None of the above</t>
+          <t>Supreme Court order</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Prime Minister’s executive powers</t>
+          <t>Collegium recommendations</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Judicial review can check executive actions including PM’s decisions.</t>
+          <t>Executive follows collegium’s advice.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which article provides for the removal of Supreme Court judges?</t>
+          <t>Which body nominates the members of the collegium?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Article 226</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Supreme Court itself</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>It describes the impeachment process.</t>
+          <t>Collegium is composed of judges only.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
+          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Judicial Collegium</t>
+          <t>PM can remove judges by ordinance</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>President can remove judges on PM advice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>PM can suspend judges</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only Parliament can remove judges by impeachment</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
+          <t>Removal requires a two-thirds majority in Parliament.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Who initiates impeachment proceedings against a Supreme Court judge?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2486,1367 +2486,1367 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Lok Sabha members</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Any member of Parliament</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>On the advice of the PM.</t>
+          <t>Any MP can initiate impeachment; PM plays advisory role.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the role of the Prime Minister in judicial impeachments?</t>
+          <t>The role of the Prime Minister in judicial appointments is primarily exercised through</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Can impeach judges</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Decides final removal</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Recommends removal to the President</t>
+          <t>Presidential advice</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>PM can recommend initiating impeachment proceedings.</t>
+          <t>PM influences appointments by advising the President.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which body was created to replace the collegium system but later struck down by the Supreme Court?</t>
+          <t>Which article protects judges from arbitrary removal by the executive?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Judicial Selection Committee</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Judicial Review Board</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>NJAC was declared unconstitutional.</t>
+          <t>Separation of judiciary from executive ensures protection.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Supreme Court Advocates-on-Record Association case dealt with which aspect of judiciary?</t>
+          <t>The Supreme Court can strike down laws passed by the executive on grounds of</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Judicial appointments</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Inefficiency</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Unpopularity</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>Opposition protests</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Collegium system</t>
+          <t>Unconstitutionality</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It upheld the collegium system against NJAC.</t>
+          <t>Judicial review protects Constitution.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who appoints the Lokpal and Lokayuktas?</t>
+          <t>Which of the following is true about the NJAC?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>It was accepted</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>It replaced the collegium system</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Central Government</t>
+          <t>It empowered PM</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It was rejected by Supreme Court</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Appointments are made by the President based on recommendations.</t>
+          <t>It was struck down for undermining judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who acts as the constitutional head of the judiciary?</t>
+          <t>Which article explicitly mentions consultation with the CJI for appointing High Court judges?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CJI is head of judiciary as per convention.</t>
+          <t>It mandates consultation with CJI, Governor, and others.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Prime Minister’s executive powers can be reviewed by judiciary under which concept?</t>
+          <t>Which constitutional article mandates the appointment of High Court judges by the President?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Executive privilege</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Parliamentary oversight</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Federalism</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Courts check constitutionality of executive actions.</t>
+          <t>It requires consultation with CJI and Governor.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Prime Minister’s advice to the President regarding judiciary appointments is generally based on</t>
+          <t>The Supreme Court’s power of judicial review limits the</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cabinet’s consensus</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>President’s powers</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Parliament’s decision</t>
+          <t>Parliament’s legislative powers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Supreme Court order</t>
+          <t>None of the above</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Collegium recommendations</t>
+          <t>Prime Minister’s executive powers</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Executive follows collegium’s advice.</t>
+          <t>Judicial review can check executive actions including PM’s decisions.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which body nominates the members of the collegium?</t>
+          <t>Which article provides for the removal of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Supreme Court itself</t>
+          <t>Article 124(4)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Collegium is composed of judges only.</t>
+          <t>It describes the impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of the following statements is true regarding the removal of Supreme Court judges?</t>
+          <t>The Prime Minister’s role in the appointment of Supreme Court judges is primarily exercised through which authority?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PM can remove judges by ordinance</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>President can remove judges on PM advice</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PM can suspend judges</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Only Parliament can remove judges by impeachment</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Removal requires a two-thirds majority in Parliament.</t>
+          <t>The PM advises the President who makes appointments based on collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Prime Minister’s influence on judiciary appointments has been curtailed since</t>
+          <t>Can the Prime Minister veto a Supreme Court judge appointment?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>Only in consultation with Cabinet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>Only with President’s approval</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>After the S.P. Gupta case, judicial independence increased.</t>
+          <t>The PM cannot veto; President follows collegium recommendations.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Under which article can the Parliament remove a Supreme Court judge?</t>
+          <t>The principle of judicial independence restricts which power of the Prime Minister?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Controlling court procedures</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Appointing judges</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Impeachment of judges</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Article 311(2)</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Impeachment procedure is mentioned in Article 124(4).</t>
+          <t>Judicial independence limits executive interference.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The appointment of High Court judges involves consultation with</t>
+          <t>Which constitutional amendment tried to limit judicial review but was struck down?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chief Justice of India only</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>State Governor only</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chief Justice of India and State Governor</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Both are consulted for High Court appointments.</t>
+          <t>It tried to curtail judiciary’s power but was struck down.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which body consults the Prime Minister on judicial appointments?</t>
+          <t>The President appoints Supreme Court judges after consultation with</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Supreme Court Collegium</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No formal consultation</t>
+          <t>Chief Justice of India and senior judges</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>There is no formal role for PM in collegium consultations.</t>
+          <t>Consultation is constitutionally mandated.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The judiciary’s independence from the Prime Minister is safeguarded by</t>
+          <t>The Prime Minister is accountable to the judiciary in matters of</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Constitutional provisions</t>
+          <t>Budgetary sanctions</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Foreign policy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Election conduct</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Legality of actions</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>These collectively protect judicial independence.</t>
+          <t>Judiciary can review legality of executive acts.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The principle of separation of powers restricts which power of the Prime Minister?</t>
+          <t>What role does the PM play in judicial accountability?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Appointing judges directly</t>
+          <t>Can remove judges</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Forming judiciary</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Removing judges directly</t>
+          <t>Direct supervision</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Recommends impeachment</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Judiciary is independent from executive.</t>
+          <t>PM can initiate impeachment recommendation to Parliament.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The President can reject collegium recommendations for judicial appointments</t>
+          <t>The impeachment of a Supreme Court judge requires what majority in Parliament?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Multiple times</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Three-fourths majority</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Unanimous approval</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Two-thirds majority</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Rejection can be sent back once for reconsideration.</t>
+          <t>It requires a special majority.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which body was proposed to replace the collegium system?</t>
+          <t>The PM’s role in judicial appointments is</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Judicial Appointment Commission</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Decisive</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Supreme Judicial Council</t>
+          <t>Constitutionally mandated</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Parliamentary Judicial Panel</t>
+          <t>Non-existent</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>National Judicial Appointments Commission</t>
+          <t>Nominal</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>NJAC was proposed but struck down by SC.</t>
+          <t>PM advises President but actual appointment is collegium-based.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The removal of a Supreme Court judge requires a</t>
+          <t>The Supreme Court can review actions of the Prime Minister under</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Simple majority in Parliament</t>
+          <t>Article 131</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Majority in Supreme Court</t>
+          <t>Article 142</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Presidential order</t>
+          <t>Article 226</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Special majority in Parliament</t>
+          <t>Article 32</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Impeachment requires two-thirds majority in both Houses.</t>
+          <t>Under fundamental rights enforcement, judiciary can review executive.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which body can challenge the PM’s recommendation on judicial appointments?</t>
+          <t>Which of the following is NOT true about the collegium system?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>It consists of the CJI and four senior judges</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>It was created by a Supreme Court judgment</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>No formal body</t>
+          <t>It recommends appointments of judges</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>It involves the Prime Minister directly</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Judicial appointments can be challenged in SC.</t>
+          <t>The PM is not part of the collegium.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Is the Prime Minister part of the Judicial Appointment Committee?</t>
+          <t>Which of the following is true regarding the PM and judiciary?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PM can remove judges directly</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PM heads judiciary</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Only for High Court appointments</t>
+          <t>PM appoints judges by executive order</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PM’s role is limited to advising President on appointments</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The collegium is independent of the executive.</t>
+          <t>PM recommends appointments but cannot directly appoint or remove judges.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The power of judicial review ensures that the Prime Minister’s actions are</t>
+          <t>Which Supreme Court judgment struck down the National Judicial Appointments Commission?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Always approved</t>
+          <t>S.P. Gupta case</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Never questioned</t>
+          <t>Minerva Mills case</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Controlled by legislature</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Subject to judicial scrutiny</t>
+          <t>NJAC case</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Judiciary can invalidate unconstitutional executive actions.</t>
+          <t>The NJAC was struck down for violating judicial independence.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Under which Article can a Supreme Court judge be removed?</t>
+          <t>Can the Prime Minister reject the recommendations made by the collegium for judicial appointments?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>No, never</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Yes, twice</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Yes, once</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>It outlines the impeachment procedure.</t>
+          <t>The President can send recommendations back once on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which body has the final say in the appointment of Supreme Court judges?</t>
+          <t>The Prime Minister’s role in judicial appointments is mostly through</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Direct appointment</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Parliament approval</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Cabinet recommendation to the President</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>But President acts on collegium recommendations.</t>
+          <t>PM advises the President via Cabinet for appointments.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which article allows Parliament to legislate on judiciary-related matters?</t>
+          <t>Which article of the Constitution deals with the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Article 247</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Article 312</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Article 122</t>
+          <t>Article 130</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Article 246</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Parliament can legislate on judiciary subject under this article.</t>
+          <t>It specifically provides for appointment of the CJI by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Can the Prime Minister unilaterally appoint Supreme Court judges?</t>
+          <t>Which Supreme Court judgment affirmed the primacy of the judiciary in appointments over the executive?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>S. P. Gupta Case</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Only for Chief Justice</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Only with Parliament approval</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Appointments require consultation and collegium recommendations.</t>
+          <t>This judgment reinforced the collegium system, limiting executive interference.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which of the following is true about the Prime Minister’s role in judicial appointments?</t>
+          <t>What is the maximum time the President can delay appointing a judge after receiving collegium recommendations?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Direct appointment authority</t>
+          <t>30 days</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Consults the Collegium</t>
+          <t>60 days</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>No role</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Recommends to President</t>
+          <t>No fixed time</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PM recommends to President but must follow Collegium advice.</t>
+          <t>The Constitution does not specify a time limit.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Appointment of Attorney General is done by</t>
+          <t>The collegium system in India was established through judgments related to which constitutional issue?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Separation of powers</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Judicial independence</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Basic structure doctrine</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>President appoints AG on PM’s advice.</t>
+          <t>Collegium protects judicial independence under basic structure.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The NJAC Act was struck down by the Supreme Court for violating</t>
+          <t>Which constitutional article provides immunity to judges from executive interference?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Judicial independence</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Article 211</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Basic structure of the Constitution</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 122</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 50</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>It was struck down as it compromised judiciary’s independence.</t>
+          <t>It mandates separation of judiciary from executive.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which constitutional principle limits the PM’s power over the judiciary?</t>
+          <t>Who is the final authority in the appointment of High Court judges?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Separation of powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Basic structure doctrine</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Multiple principles safeguard judicial independence.</t>
+          <t>Appointment is made by the President after consultation.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The President can reject a recommendation for appointment of a Supreme Court judge once</t>
+          <t>Which constitutional body recommends appointments of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Parliamentary Committee</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes, twice</t>
+          <t>Judicial Commission</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yes, thrice</t>
+          <t>Union Cabinet</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes, once</t>
+          <t>Collegium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>The President can send back recommendations once for reconsideration.</t>
+          <t>The Collegium system recommends judges’ appointments.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article requires the President to consult the Chief Justice of India in appointing Supreme Court judges?</t>
+          <t>Which case emphasized the independence of the judiciary from the executive?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 148</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 124(2)</t>
+          <t>S.P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>It mandates consultation before appointment.</t>
+          <t>Known as the Judges’ Transfer case affirming independence.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Who acts as the guardian of the independence of the judiciary?</t>
+          <t>Who appoints the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>President</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court Collegium</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>CJI protects judiciary’s independence.</t>
+          <t>The President appoints CJI after consultation with senior judges.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The PM’s cabinet is involved in which stage of judicial appointments?</t>
+          <t>The Prime Minister’s office can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Consultation</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>Direct orders</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Judicial Collegium</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No involvement</t>
+          <t>Parliamentary resolution</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Recommendation to President</t>
+          <t>Cabinet advice to President</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Cabinet advises President on appointments.</t>
+          <t>PM influences President through Cabinet advice.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who appoints the Attorney General of India?</t>
+          <t>Who is responsible for the administration of the Supreme Court?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Prime Minister directly</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>President on PM’s advice</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>The President appoints AG following PM’s advice.</t>
+          <t>CJI oversees the administration of the Supreme Court.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The collegium system is criticized for</t>
+          <t>The PM can influence judiciary appointments through</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Excessive executive control</t>
+          <t>Control over Collegium</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Political interference</t>
+          <t>Control over Parliament</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Parliamentary involvement</t>
+          <t>Control over Election Commission</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lack of transparency</t>
+          <t>Control over President</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Its opaque functioning is often criticized.</t>
+          <t>President acts on PM’s advice.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which case established the “Basic Structure Doctrine” limiting Parliament and executive powers?</t>
+          <t>Which landmark case established the Collegium system?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3926,547 +3926,547 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t>S. P. Gupta v. Union of India</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Indira Gandhi v. Raj Narain</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>Minerva Mills</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Golak Nath</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>S. R. Bommai</t>
-        </is>
-      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati</t>
+          <t>S. P. Gupta v. Union of India</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>It asserted constitutional amendments cannot alter the basic structure.</t>
+          <t>It reinforced judiciary’s primacy in appointments.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which is the primary criteria for appointing judges as per collegium recommendations?</t>
+          <t>Which of the following is NOT a feature of the collegium system?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seniority</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Confidential recommendations</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Political affiliation</t>
+          <t>Collegium consists of CJI and senior judges</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Executive preference</t>
+          <t>No formal legal backing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Merit</t>
+          <t>Executive involvement in selection</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Judges are appointed based on merit and integrity.</t>
+          <t>The executive has no formal role in selection.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who has the final say in appointment of Supreme Court judges?</t>
+          <t>The power of judicial review can invalidate actions by the Prime Minister under which condition?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>If unpopular</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Collegium</t>
+          <t>If advised by Parliament</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>If voted by Lok Sabha</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>If unconstitutional</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>President appoints judges but follows collegium recommendations.</t>
+          <t>Judiciary ensures constitutional compliance.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which article states the conditions for removal of High Court judges?</t>
+          <t>Which amendment added the 10th Schedule (anti-defection law) affecting MPs and indirectly affecting judiciary?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Article 311</t>
+          <t>61st Amendment</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Article 227</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Article 217(1)(b)</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>It provides the removal process for High Court judges.</t>
+          <t>Added anti-defection law which can involve judicial scrutiny.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who presides over the Supreme Court when the Chief Justice of India is absent?</t>
+          <t>Which Article lays down the procedure for consultation with Chief Justice in appointing judges?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 222</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 230</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Senior-most judge</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>The senior-most puisne judge acts as CJI.</t>
+          <t>It requires consultation with CJI before appointment.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Under the collegium system, how many judges (including CJI) recommend appointments to the Supreme Court?</t>
+          <t>The PM’s influence on judiciary appointments has</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Increased over time</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Remained constant</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Never existed</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Reduced over time</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>The collegium consists of the CJI and four senior-most judges.</t>
+          <t>Collegium system reduces direct PM influence.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>In the impeachment process of a judge, who investigates the charges?</t>
+          <t>What is the role of the Prime Minister in the impeachment of a judge?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Initiate impeachment</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Preside over proceedings</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Parliamentary committee</t>
+          <t>Recommend removal</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A committee constituted by Parliament investigates.</t>
+          <t>The PM may advise the President to initiate proceedings.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which constitutional principle restricts the Prime Minister's direct control over judicial appointments?</t>
+          <t>Who appoints the Registrar General of the Supreme Court?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Separation of Powers</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Basic Structure Doctrine</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Judicial Review</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>These principles collectively limit executive control.</t>
+          <t>CJI appoints administrative officers.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who is the custodian of judicial independence in India?</t>
+          <t>Which constitutional article governs the appointment of the Chief Justice of India?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 217</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 311</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 124(2)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>CJI safeguards judicial independence.</t>
+          <t>It provides for President’s appointment after consultation.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which of the following is a check on the PM’s power regarding judiciary?</t>
+          <t>The collegium system was challenged in which case?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Parliamentary approval</t>
+          <t>Indira Gandhi v. Raj Narain</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Public opinion</t>
+          <t>Minerva Mills</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Kesavananda Bharati</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Judicial review</t>
+          <t>Supreme Court Advocates-on-Record Association v. Union of India</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Supreme Court can review executive actions.</t>
+          <t>The NJAC case questioned collegium’s legitimacy.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which constitutional amendment added the anti-defection law affecting Parliament members?</t>
+          <t>Who among the following has no direct role in the appointment of Supreme Court judges?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>42nd</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>44th</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61st</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>52nd</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>It was added by the 52nd Amendment.</t>
+          <t>Parliament does not participate in appointments.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The PM can recommend removal of a Supreme Court judge under</t>
+          <t>What is the role of the Prime Minister during judicial review of executive actions?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>No role</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Article 217</t>
+          <t>Can override judicial orders</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Approves court judgments</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Article 124(4)</t>
+          <t>Subject to judicial orders</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Removal requires Parliament process initiated by PM’s recommendation.</t>
+          <t>Executive actions including PM’s are subject to judicial review.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The principle of separation of powers implies the PM should</t>
+          <t>The Prime Minister’s influence on judicial appointments</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Directly control judiciary</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Influence judiciary indirectly</t>
+          <t>Has increased over years</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>Remains constant</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Appoint judges directly</t>
+          <t>Is absolute</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Not interfere in judiciary</t>
+          <t>Has reduced after collegium system</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Separation mandates judicial independence.</t>
+          <t>Collegium limits executive role.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who is the appointing authority for the Attorney General of India?</t>
+          <t>The role of the PM in judiciary is</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Legislative</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Judicial</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Advisory</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Appointed by the President on PM’s advice.</t>
+          <t>PM’s role is advisory via President.</t>
         </is>
       </c>
     </row>
